--- a/00-TrainRnns/tau-6/Y_otm/Metricas.xlsx
+++ b/00-TrainRnns/tau-6/Y_otm/Metricas.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,10 +474,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9994188277498586</v>
+        <v>0.9976234497654145</v>
       </c>
       <c r="E2" t="n">
-        <v>4.552148894450943e-05</v>
+        <v>0.000186473242072434</v>
       </c>
     </row>
     <row r="3">
@@ -493,14 +493,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>model_arch21_r0.9_Ld0.5_Lp0.5_seed5011</t>
+          <t>model_arch79_r0.9_Ld0.5_Lp0.5_seed922</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9957674201010379</v>
+        <v>0.9905754297957913</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0003315253593585621</v>
+        <v>0.000739487907952663</v>
       </c>
     </row>
     <row r="4">
@@ -516,14 +516,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>model_arch4_r0.9_Ld0.7_Lp0.3_seed9974</t>
+          <t>model_arch21_r0.9_Ld0.5_Lp0.5_seed5011</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9988865761514648</v>
+        <v>0.9936864007351381</v>
       </c>
       <c r="E4" t="n">
-        <v>8.721116914876299e-05</v>
+        <v>0.0004953892019329645</v>
       </c>
     </row>
     <row r="5">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.998170346066948</v>
+        <v>0.9892883992583934</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001433113354353053</v>
+        <v>0.0008404732578359393</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +562,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ENSEMBLE</t>
+          <t>model_arch94_r0.9_Ld0.3_Lp0.7_seed1932</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9994713965688482</v>
+        <v>0.9938342822925865</v>
       </c>
       <c r="E6" t="n">
-        <v>4.140393014524195e-05</v>
+        <v>0.00048378584802156</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ZZx2</t>
+          <t>ZZx1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,14 +585,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>model_arch17_r0.01_Ld0.5_Lp0.5_seed6686</t>
+          <t>ENSEMBLE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9911830942707265</v>
+        <v>0.9945478829300546</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005194387783101885</v>
+        <v>0.0004277940063692697</v>
       </c>
     </row>
     <row r="8">
@@ -608,14 +608,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>model_arch21_r0.9_Ld0.5_Lp0.5_seed5011</t>
+          <t>model_arch17_r0.01_Ld0.5_Lp0.5_seed6686</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.9871817620484028</v>
+        <v>0.9917017554700374</v>
       </c>
       <c r="E8" t="n">
-        <v>0.007551730806829908</v>
+        <v>0.004897047954838462</v>
       </c>
     </row>
     <row r="9">
@@ -631,14 +631,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>model_arch4_r0.9_Ld0.7_Lp0.3_seed9974</t>
+          <t>model_arch79_r0.9_Ld0.5_Lp0.5_seed922</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.9641233901295312</v>
+        <v>0.9850328144350909</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02113632942581454</v>
+        <v>0.008832594074045205</v>
       </c>
     </row>
     <row r="10">
@@ -654,14 +654,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>model_arch43_r0.9_Ld0.7_Lp0.3_seed9974</t>
+          <t>model_arch21_r0.9_Ld0.5_Lp0.5_seed5011</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9603017077503203</v>
+        <v>0.9757969685614253</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02338783362366023</v>
+        <v>0.01428294926465573</v>
       </c>
     </row>
     <row r="11">
@@ -677,20 +677,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ENSEMBLE</t>
+          <t>model_arch43_r0.9_Ld0.7_Lp0.3_seed9974</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9898252977933704</v>
+        <v>0.9532227946391086</v>
       </c>
       <c r="E11" t="n">
-        <v>0.005994319374805433</v>
+        <v>0.02760465987938819</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ZZxReto</t>
+          <t>ZZx2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -700,20 +700,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>model_arch17_r0.01_Ld0.5_Lp0.5_seed6686</t>
+          <t>model_arch94_r0.9_Ld0.3_Lp0.7_seed1932</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.922727592494359</v>
+        <v>0.9406597084818573</v>
       </c>
       <c r="E12" t="n">
-        <v>0.006319946563230323</v>
+        <v>0.0350185213473997</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ZZxReto</t>
+          <t>ZZx2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -723,14 +723,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>model_arch21_r0.9_Ld0.5_Lp0.5_seed5011</t>
+          <t>ENSEMBLE</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.8466944289482148</v>
+        <v>0.9817255020129619</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01253853798747066</v>
+        <v>0.01078434031077263</v>
       </c>
     </row>
     <row r="14">
@@ -746,14 +746,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>model_arch4_r0.9_Ld0.7_Lp0.3_seed9974</t>
+          <t>model_arch17_r0.01_Ld0.5_Lp0.5_seed6686</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.8258898824492689</v>
+        <v>0.8599166837379482</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01424009778597933</v>
+        <v>0.01146821135422913</v>
       </c>
     </row>
     <row r="15">
@@ -769,14 +769,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>model_arch43_r0.9_Ld0.7_Lp0.3_seed9974</t>
+          <t>model_arch79_r0.9_Ld0.5_Lp0.5_seed922</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.8546708083780734</v>
+        <v>0.6796420747080592</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01188616680619128</v>
+        <v>0.02622676628655444</v>
       </c>
     </row>
     <row r="16">
@@ -792,14 +792,1049 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>model_arch21_r0.9_Ld0.5_Lp0.5_seed5011</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.741589784886736</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0211552884532441</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ZZxReto</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>model_arch43_r0.9_Ld0.7_Lp0.3_seed9974</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.6593238980516605</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.02789015597810236</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ZZxReto</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>model_arch94_r0.9_Ld0.3_Lp0.7_seed1932</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.7558731501615169</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.01998595111749444</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ZZxReto</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>ENSEMBLE</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>0.8737047361781646</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.01032942216126511</v>
+      <c r="D19" t="n">
+        <v>0.7526241268756242</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.02025193915041427</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ZZy1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>model_arch17_r0.01_Ld0.5_Lp0.5_seed6686</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-4.094983594426739</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.6485383724729805</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ZZy1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>model_arch79_r0.9_Ld0.5_Lp0.5_seed922</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-6.151127184403403</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9102640468937742</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ZZy1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>model_arch21_r0.9_Ld0.5_Lp0.5_seed5011</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-7.849378086924341</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.126433707886691</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ZZy1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>model_arch43_r0.9_Ld0.7_Lp0.3_seed9974</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-5.841538468700373</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.8708566262226515</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ZZy1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>model_arch94_r0.9_Ld0.3_Lp0.7_seed1932</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-6.967594061506444</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.014191780877789</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ZZy1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ENSEMBLE</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-6.088319461887497</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9022692776498147</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ZZy2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>model_arch17_r0.01_Ld0.5_Lp0.5_seed6686</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-30.18920439309159</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.949241124288469</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ZZy2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>model_arch79_r0.9_Ld0.5_Lp0.5_seed922</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-34.40404700900184</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.212657415893382</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ZZy2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>model_arch21_r0.9_Ld0.5_Lp0.5_seed5011</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>-24.13748248742893</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.571024833080736</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ZZy2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>model_arch43_r0.9_Ld0.7_Lp0.3_seed9974</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-41.9422089771274</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.683772200503672</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ZZy2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>model_arch94_r0.9_Ld0.3_Lp0.7_seed1932</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>-30.98990713895263</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.999282885562404</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ZZy2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ENSEMBLE</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>-32.04394858866362</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.065157632304465</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LSG-1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>model_arch17_r0.01_Ld0.5_Lp0.5_seed6686</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.05850319293366613</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.3878947334832108</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LSG-1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>model_arch79_r0.9_Ld0.5_Lp0.5_seed922</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1100222903375275</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.3261375769106037</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LSG-1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>model_arch21_r0.9_Ld0.5_Lp0.5_seed5011</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.06915846234054157</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.3411123675166326</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>LSG-1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>model_arch43_r0.9_Ld0.7_Lp0.3_seed9974</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.001399912865584829</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.3659428873159662</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LSG-1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>model_arch94_r0.9_Ld0.3_Lp0.7_seed1932</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.01039622342895719</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.3626461362890374</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LSG-1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ENSEMBLE</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.03108989200216117</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.3550628194794339</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LSG-2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>model_arch17_r0.01_Ld0.5_Lp0.5_seed6686</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.8309710211728538</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.0142167197670747</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>LSG-2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>model_arch79_r0.9_Ld0.5_Lp0.5_seed922</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.1176817069383558</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.07421018576139299</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LSG-2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>model_arch21_r0.9_Ld0.5_Lp0.5_seed5011</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.1597362685335477</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.09754330676229823</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LSG-2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>model_arch43_r0.9_Ld0.7_Lp0.3_seed9974</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>-0.07203339757651617</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.09016677791017109</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>LSG-2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>model_arch94_r0.9_Ld0.3_Lp0.7_seed1932</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.4857431201655252</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.04325321018695508</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>LSG-2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ENSEMBLE</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.3498419993410986</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.05468360611195218</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ZZx1-inv</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>model_arch17_r0.01_Ld0.5_Lp0.5_seed6686</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>-1.425781432098335</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.1622218731735266</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ZZx1-inv</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>model_arch79_r0.9_Ld0.5_Lp0.5_seed922</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>-1.664602490987981</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.1781928089774383</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ZZx1-inv</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>model_arch21_r0.9_Ld0.5_Lp0.5_seed5011</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>-1.042305166885863</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.1365772552218819</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ZZx1-inv</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>model_arch43_r0.9_Ld0.7_Lp0.3_seed9974</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>-2.235421699451188</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.2163658117117495</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ZZx1-inv</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>model_arch94_r0.9_Ld0.3_Lp0.7_seed1932</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>-0.8900207866516747</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.1263933791769201</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ZZx1-inv</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ENSEMBLE</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>-1.419671955961826</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.1618133076490902</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>zzx2-inv2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>model_arch17_r0.01_Ld0.5_Lp0.5_seed6686</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>-0.04209252760422899</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.6340559320421291</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>zzx2-inv2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>model_arch79_r0.9_Ld0.5_Lp0.5_seed922</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>-0.2515674149098419</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.7615098686089048</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>zzx2-inv2</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>model_arch21_r0.9_Ld0.5_Lp0.5_seed5011</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>-0.07678248204875882</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.6551628595127567</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>zzx2-inv2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>model_arch43_r0.9_Ld0.7_Lp0.3_seed9974</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>-0.07510397088819887</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.6541415778797343</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>zzx2-inv2</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>model_arch94_r0.9_Ld0.3_Lp0.7_seed1932</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>-0.4535892673058135</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.8844290437499946</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>zzx2-inv2</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ENSEMBLE</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>-0.1697460356297678</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.7117260638831666</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>semiCirc</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>model_arch17_r0.01_Ld0.5_Lp0.5_seed6686</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>-2.974263292791399</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.6037608412087754</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>semiCirc</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>model_arch79_r0.9_Ld0.5_Lp0.5_seed922</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>-1.442345866066331</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.3710355067047596</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>semiCirc</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>model_arch21_r0.9_Ld0.5_Lp0.5_seed5011</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>-0.909860509692757</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.2901415691343435</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>semiCirc</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>model_arch43_r0.9_Ld0.7_Lp0.3_seed9974</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>-1.169801302514533</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.3296311701437222</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>semiCirc</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>model_arch94_r0.9_Ld0.3_Lp0.7_seed1932</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>-1.364798321144123</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.3592546639405595</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>semiCirc</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ENSEMBLE</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>-1.502873691953639</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.380230753315759</v>
       </c>
     </row>
   </sheetData>
@@ -813,7 +1848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -849,14 +1884,19 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>model_arch4_r0.9_Ld0.7_Lp0.3_seed9974</t>
+          <t>model_arch79_r0.9_Ld0.5_Lp0.5_seed922</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>model_arch94_r0.9_Ld0.3_Lp0.7_seed1932</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ZZx1</t>
+          <t>LSG-1</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -865,25 +1905,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9994713965688482</v>
+        <v>0.03108989200216117</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9994188277498586</v>
+        <v>-0.05850319293366613</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9957674201010379</v>
+        <v>0.06915846234054157</v>
       </c>
       <c r="F2" t="n">
-        <v>0.998170346066948</v>
+        <v>0.001399912865584829</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9988865761514648</v>
+        <v>0.1100222903375275</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.01039622342895719</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ZZx2</t>
+          <t>LSG-2</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
@@ -892,46 +1935,262 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9898252977933704</v>
+        <v>0.3498419993410986</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9911830942707265</v>
+        <v>0.8309710211728538</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9871817620484028</v>
+        <v>-0.1597362685335477</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9603017077503203</v>
+        <v>-0.07203339757651617</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9641233901295312</v>
+        <v>0.1176817069383558</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4857431201655252</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
+          <t>ZZx1</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9945478829300546</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9976234497654145</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9936864007351381</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9892883992583934</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9905754297957913</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9938342822925865</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>ZZx1-inv</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.419671955961826</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.425781432098335</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-1.042305166885863</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-2.235421699451188</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-1.664602490987981</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.8900207866516747</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ZZx2</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9817255020129619</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9917017554700374</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9757969685614253</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9532227946391086</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9850328144350909</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9406597084818573</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
           <t>ZZxReto</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.8737047361781646</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.922727592494359</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.8466944289482148</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.8546708083780734</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.8258898824492689</v>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.7526241268756242</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.8599166837379482</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.741589784886736</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6593238980516605</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6796420747080592</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7558731501615169</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>ZZy1</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>-6.088319461887497</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-4.094983594426739</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-7.849378086924341</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-5.841538468700373</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-6.151127184403403</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-6.967594061506444</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ZZy2</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-32.04394858866362</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-30.18920439309159</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-24.13748248742893</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-41.9422089771274</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-34.40404700900184</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-30.98990713895263</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>semiCirc</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.502873691953639</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.974263292791399</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.909860509692757</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1.169801302514533</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1.442345866066331</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-1.364798321144123</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>zzx2-inv2</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.1697460356297678</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.04209252760422899</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.07678248204875882</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.07510397088819887</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.2515674149098419</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.4535892673058135</v>
       </c>
     </row>
   </sheetData>
@@ -945,7 +2204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -981,14 +2240,19 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>model_arch4_r0.9_Ld0.7_Lp0.3_seed9974</t>
+          <t>model_arch79_r0.9_Ld0.5_Lp0.5_seed922</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>model_arch94_r0.9_Ld0.3_Lp0.7_seed1932</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ZZx1</t>
+          <t>LSG-1</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -997,25 +2261,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.140393014524195e-05</v>
+        <v>0.3550628194794339</v>
       </c>
       <c r="D2" t="n">
-        <v>4.552148894450943e-05</v>
+        <v>0.3878947334832108</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0003315253593585621</v>
+        <v>0.3411123675166326</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001433113354353053</v>
+        <v>0.3659428873159662</v>
       </c>
       <c r="G2" t="n">
-        <v>8.721116914876299e-05</v>
+        <v>0.3261375769106037</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3626461362890374</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ZZx2</t>
+          <t>LSG-2</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
@@ -1024,46 +2291,262 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.005994319374805433</v>
+        <v>0.05468360611195218</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005194387783101885</v>
+        <v>0.0142167197670747</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007551730806829908</v>
+        <v>0.09754330676229823</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02338783362366023</v>
+        <v>0.09016677791017109</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02113632942581454</v>
+        <v>0.07421018576139299</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.04325321018695508</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
+          <t>ZZx1</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0004277940063692697</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.000186473242072434</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0004953892019329645</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0008404732578359393</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.000739487907952663</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.00048378584802156</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>ZZx1-inv</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.1618133076490902</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1622218731735266</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1365772552218819</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2163658117117495</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1781928089774383</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.1263933791769201</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ZZx2</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.01078434031077263</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.004897047954838462</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.01428294926465573</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.02760465987938819</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.008832594074045205</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0350185213473997</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
           <t>ZZxReto</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.01032942216126511</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.006319946563230323</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.01253853798747066</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.01188616680619128</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.01424009778597933</v>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.02025193915041427</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.01146821135422913</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0211552884532441</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.02789015597810236</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.02622676628655444</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.01998595111749444</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>ZZy1</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9022692776498147</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6485383724729805</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.126433707886691</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8708566262226515</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9102640468937742</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.014191780877789</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ZZy2</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2.065157632304465</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.949241124288469</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.571024833080736</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.683772200503672</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.212657415893382</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.999282885562404</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>semiCirc</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.380230753315759</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6037608412087754</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.2901415691343435</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3296311701437222</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.3710355067047596</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3592546639405595</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>zzx2-inv2</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.7117260638831666</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6340559320421291</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.6551628595127567</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6541415778797343</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7615098686089048</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.8844290437499946</v>
       </c>
     </row>
   </sheetData>
